--- a/assets/downloads/CONFIG MAKER EN by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER EN by KJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="933" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{228E9659-551D-4514-AD01-03960FBA2CCE}"/>
+  <xr:revisionPtr revIDLastSave="953" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA81C205-A9C8-49FE-9E79-DA35905604AC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Total</t>
   </si>
@@ -68,9 +68,6 @@
     <t>SETUP</t>
   </si>
   <si>
-    <t>OPT</t>
-  </si>
-  <si>
     <t>OPT1</t>
   </si>
   <si>
@@ -86,15 +83,9 @@
     <t>SSD</t>
   </si>
   <si>
-    <t>CONFIG MAKER 2024.7.18</t>
-  </si>
-  <si>
     <t>by KJ</t>
   </si>
   <si>
-    <t>https://kevinjmt.github.io/</t>
-  </si>
-  <si>
     <t>CONFIG MAKER v2024.7.18</t>
   </si>
   <si>
@@ -177,6 +168,18 @@
   </si>
   <si>
     <t>OPT5</t>
+  </si>
+  <si>
+    <t>CONFIG NAME</t>
+  </si>
+  <si>
+    <t>DOWNLOAD AGAIN</t>
+  </si>
+  <si>
+    <t>OPTS</t>
+  </si>
+  <si>
+    <t>OS</t>
   </si>
 </sst>
 </file>
@@ -501,27 +504,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$17" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$25" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$30" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -916,13 +923,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1366,13 +1373,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1416,13 +1423,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1466,13 +1473,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1514,13 +1521,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1559,13 +1566,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1604,13 +1611,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1649,13 +1656,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1694,13 +1701,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>184150</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1741,13 +1748,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1791,13 +1798,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1841,13 +1848,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1891,13 +1898,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -1941,13 +1948,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2041,13 +2048,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>19050</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2091,13 +2098,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2108,7 +2115,7 @@
                   <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60A94078-977C-4D13-8E33-33D090711893}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2141,13 +2148,13 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>12700</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
@@ -2158,7 +2165,57 @@
                   <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEDAAB99-9B56-4EC1-8CAA-0AB9DD78F321}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1093" name="Spinner 69" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A98AC2B7-CDF6-EFF3-0CAD-A82E060FDC72}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2509,7 +2566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3D32E-9FFB-480D-9074-7649C0A05B73}">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.81640625" customWidth="1"/>
@@ -2525,7 +2582,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -2537,7 +2594,7 @@
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="28">
@@ -2554,22 +2611,22 @@
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>0</v>
@@ -2579,7 +2636,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="13"/>
       <c r="B4" s="16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -2600,7 +2657,7 @@
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="13"/>
       <c r="B5" s="16" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
@@ -2614,14 +2671,14 @@
         <v>0</v>
       </c>
       <c r="H5" s="16">
-        <f t="shared" ref="H5:H12" si="0">(E5*F5)+G5</f>
+        <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="13"/>
       <c r="B6" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -2642,7 +2699,7 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="13"/>
       <c r="B7" s="16" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2663,7 +2720,7 @@
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>
       <c r="B8" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -2705,7 +2762,7 @@
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>
       <c r="B10" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -2726,7 +2783,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>
       <c r="B11" s="16" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -2747,7 +2804,7 @@
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>
       <c r="B12" s="16" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -2765,70 +2822,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="19" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16">
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="16">
-        <v>0</v>
-      </c>
-      <c r="F16" s="16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="16">
-        <v>0</v>
-      </c>
-      <c r="H16" s="16">
-        <f>(E16*F16)+G16</f>
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -2842,13 +2899,14 @@
         <v>0</v>
       </c>
       <c r="H17" s="16">
+        <f>(E17*F17)+G17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
       <c r="B18" s="16" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -2862,14 +2920,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="16">
-        <f t="shared" ref="H18:H21" si="1">(E18*F18)+G18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
       <c r="B19" s="16" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -2883,13 +2940,14 @@
         <v>0</v>
       </c>
       <c r="H19" s="16">
+        <f t="shared" ref="H19:H22" si="1">(E19*F19)+G19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="16" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2903,14 +2961,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="16">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -2928,84 +2985,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="13"/>
+      <c r="B22" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="16">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" s="16">
-        <v>0</v>
-      </c>
-      <c r="H25" s="16">
-        <f>(E25*F25)+G25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="18">
-        <f>H25-H4</f>
-        <v>0</v>
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C26" s="17"/>
-      <c r="D26" s="16"/>
+      <c r="D26" s="17"/>
       <c r="E26" s="16">
         <v>0</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="16">
@@ -3016,14 +3069,14 @@
         <v>0</v>
       </c>
       <c r="I26" s="18">
-        <f>H26-H10</f>
+        <f>H26-H4</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="16"/>
@@ -3037,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="16">
-        <f t="shared" ref="H27" si="2">(E27*F27)+G27</f>
+        <f>(E27*F27)+G27</f>
         <v>0</v>
       </c>
       <c r="I27" s="18">
@@ -3048,7 +3101,7 @@
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="16" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="16"/>
@@ -3062,18 +3115,18 @@
         <v>0</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28:H29" si="3">(E28*F28)+G28</f>
+        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
         <v>0</v>
       </c>
       <c r="I28" s="18">
-        <f>H28-H11</f>
+        <f>H28-H10</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="16" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="16"/>
@@ -3087,149 +3140,174 @@
         <v>0</v>
       </c>
       <c r="H29" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="H29:H30" si="3">(E29*F29)+G29</f>
         <v>0</v>
       </c>
       <c r="I29" s="18">
-        <f>H29-H12</f>
+        <f>H29-H11</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="C30" s="4"/>
-      <c r="I30" s="5"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16">
+        <v>0</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="18">
+        <f>H30-H12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
     </row>
-    <row r="32" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="F32" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="22"/>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="6">
-        <f>SUM(H4:H12)</f>
-        <v>0</v>
-      </c>
-      <c r="C33" s="34">
-        <f>B36-B37</f>
-        <v>0</v>
-      </c>
-      <c r="D33" s="34"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
+      <c r="A33" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="F33" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B34" s="6">
-        <f>SUM(H16:H21)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="34"/>
+        <f>SUM(H4:H12)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="34">
+        <f>B37-B38</f>
+        <v>0</v>
+      </c>
       <c r="D34" s="34"/>
-      <c r="F34" s="8"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H34" s="32"/>
       <c r="I34" s="33"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" s="6">
-        <f>SUM(H25:H29)</f>
+        <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
       <c r="C35" s="34"/>
       <c r="D35" s="34"/>
-      <c r="F35" s="9"/>
+      <c r="F35" s="8"/>
       <c r="G35" s="31" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H35" s="32"/>
       <c r="I35" s="33"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B36" s="3">
-        <f>B33+B34+B35</f>
+      <c r="A36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="6">
+        <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
       <c r="C36" s="34"/>
       <c r="D36" s="34"/>
-      <c r="F36" s="10"/>
+      <c r="F36" s="9"/>
       <c r="G36" s="31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H36" s="32"/>
       <c r="I36" s="33"/>
     </row>
-    <row r="37" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="6">
+    <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="3">
+        <f>B34+B35+B36</f>
         <v>0</v>
       </c>
       <c r="C37" s="34"/>
       <c r="D37" s="34"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="32"/>
+      <c r="I37" s="33"/>
     </row>
-    <row r="38" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>17</v>
-      </c>
+    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="6">
+        <v>0</v>
+      </c>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
     </row>
+    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="15" t="s">
-        <v>18</v>
+      <c r="B40" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="15" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="C33:D37"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="F32:I32"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
-    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A24:I24"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C39" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
-    <hyperlink ref="B40" r:id="rId2" xr:uid="{12A6037E-86C9-4725-89EE-1D861E2C5CBA}"/>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
+    <hyperlink ref="B41" r:id="rId2" xr:uid="{D8547E09-E080-46C6-9411-E861E70832A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
@@ -3268,13 +3346,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>24</xdr:row>
+                    <xdr:row>25</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>25</xdr:row>
+                    <xdr:row>26</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3290,13 +3368,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>25</xdr:row>
+                    <xdr:row>26</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>26</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3488,13 +3566,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>15</xdr:row>
+                    <xdr:row>16</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3510,13 +3588,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>19</xdr:row>
                     <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3532,13 +3610,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>18</xdr:row>
+                    <xdr:row>19</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3554,13 +3632,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>19</xdr:row>
+                    <xdr:row>20</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>21</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3576,13 +3654,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>20</xdr:row>
+                    <xdr:row>21</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>21</xdr:row>
+                    <xdr:row>22</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3620,13 +3698,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>16</xdr:row>
+                    <xdr:row>17</xdr:row>
                     <xdr:rowOff>19050</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>17</xdr:row>
+                    <xdr:row>18</xdr:row>
                     <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3642,13 +3720,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>26</xdr:row>
+                    <xdr:row>27</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3664,13 +3742,13 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>27</xdr:row>
+                    <xdr:row>28</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
@@ -3686,13 +3764,35 @@
                   <from>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>6350</xdr:colOff>
-                    <xdr:row>28</xdr:row>
+                    <xdr:row>29</xdr:row>
                     <xdr:rowOff>12700</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
                     <xdr:colOff>184150</xdr:colOff>
-                    <xdr:row>29</xdr:row>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId27" name="Spinner 69">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>13</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/assets/downloads/CONFIG MAKER EN by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER EN by KJ.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="953" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA81C205-A9C8-49FE-9E79-DA35905604AC}"/>
+  <xr:revisionPtr revIDLastSave="1016" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42E49BA0-BE8A-46BA-B734-9407F93AB60C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG 1" sheetId="1" r:id="rId1"/>
+    <sheet name="CONFIG 1" sheetId="2" r:id="rId1"/>
+    <sheet name="MANUAL" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
   <si>
     <t>Total</t>
   </si>
@@ -181,6 +182,81 @@
   <si>
     <t>OS</t>
   </si>
+  <si>
+    <t>`=H26-0`</t>
+  </si>
+  <si>
+    <t>`=H26-H4`</t>
+  </si>
+  <si>
+    <t>On each line, fill in information below:</t>
+  </si>
+  <si>
+    <t>If the product is in stock</t>
+  </si>
+  <si>
+    <t>Product reference</t>
+  </si>
+  <si>
+    <t>Quantity required</t>
+  </si>
+  <si>
+    <t>Price per unit</t>
+  </si>
+  <si>
+    <t>Delivery charges for the product</t>
+  </si>
+  <si>
+    <t>Link to a price comparison website</t>
+  </si>
+  <si>
+    <t>The link to the site where the product is cheapest</t>
+  </si>
+  <si>
+    <t>Total product price, quantity and delivery applied</t>
+  </si>
+  <si>
+    <t>Total price compared to budget</t>
+  </si>
+  <si>
+    <t>⚠️ For saves ⚠️</t>
+  </si>
+  <si>
+    <t>On each line, the formula to calculate savings is as follows:</t>
+  </si>
+  <si>
+    <t>To calculate the savings, simply replace the 0</t>
+  </si>
+  <si>
+    <t>by the box you wish to compare. For example:</t>
+  </si>
+  <si>
+    <t>If OPT1 is a processor, simply set the box for the total price of the</t>
+  </si>
+  <si>
+    <t>processor (H4) instead of 0. The new formula is therefore:</t>
+  </si>
+  <si>
+    <t>All that's left to do is fill in the information above!</t>
+  </si>
+  <si>
+    <t>Total PC price</t>
+  </si>
+  <si>
+    <t>Total Setup price</t>
+  </si>
+  <si>
+    <t>Total selected options price</t>
+  </si>
+  <si>
+    <t>Total price</t>
+  </si>
+  <si>
+    <t>Fixed budget</t>
+  </si>
+  <si>
+    <t>INSTRUCTION MANUAL</t>
+  </si>
 </sst>
 </file>
 
@@ -189,7 +265,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[Red]\▲\ 0.00;[Green]\ \▼\ 0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,8 +325,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,8 +391,68 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -354,12 +512,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,7 +639,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -411,9 +660,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -437,6 +683,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -446,8 +698,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -472,47 +799,47 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$9" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
@@ -527,32 +854,124 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$26" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$27" max="100" page="10" val="0"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$9" max="100" page="10" val="0"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$18" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$28" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$29" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$30" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$13" max="100" page="10" val="0"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$4" max="100" page="10"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$5" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$6" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$7" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$8" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$11" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$10" max="100" page="10" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Spin" dx="31" fmlaLink="$E$12" max="100" page="10" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,13 +991,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1025" name="Spinner 1" hidden="1">
+        <xdr:cNvPr id="2" name="Spinner 1" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -586,8 +1005,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="933450"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -617,13 +1036,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1026" name="Spinner 2" hidden="1">
+        <xdr:cNvPr id="3" name="Spinner 2" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -631,8 +1050,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="1117600"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -662,13 +1081,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1027" name="Spinner 3" hidden="1">
+        <xdr:cNvPr id="4" name="Spinner 3" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -676,8 +1095,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="1301750"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -707,13 +1126,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1028" name="Spinner 4" hidden="1">
+        <xdr:cNvPr id="5" name="Spinner 4" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -721,8 +1140,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="1485900"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -752,13 +1171,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1029" name="Spinner 5" hidden="1">
+        <xdr:cNvPr id="6" name="Spinner 5" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1029"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -766,8 +1185,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="2038350"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -797,13 +1216,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1030" name="Spinner 6" hidden="1">
+        <xdr:cNvPr id="7" name="Spinner 6" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -811,8 +1230,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="1670050"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -842,13 +1261,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1031" name="Spinner 7" hidden="1">
+        <xdr:cNvPr id="8" name="Spinner 7" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1031"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -856,8 +1275,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="2222500"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -887,13 +1306,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1032" name="Spinner 8" hidden="1">
+        <xdr:cNvPr id="9" name="Spinner 8" hidden="1">
           <a:extLst>
             <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1032"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008040000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -901,8 +1320,8 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="5067300" y="2406650"/>
+          <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -923,24 +1342,24 @@
         <xdr:from>
           <xdr:col>4</xdr:col>
           <xdr:colOff>6350</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
           <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1036" name="Spinner 12" hidden="1">
+            <xdr:cNvPr id="2049" name="Spinner 1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1036"/>
+                  <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -984,13 +1403,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1037" name="Spinner 13" hidden="1">
+            <xdr:cNvPr id="2050" name="Spinner 2" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1037"/>
+                  <a14:compatExt spid="_x0000_s2050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1034,13 +1453,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1038" name="Spinner 14" hidden="1">
+            <xdr:cNvPr id="2051" name="Spinner 3" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1038"/>
+                  <a14:compatExt spid="_x0000_s2051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1084,13 +1503,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1040" name="Spinner 16" hidden="1">
+            <xdr:cNvPr id="2052" name="Spinner 4" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1040"/>
+                  <a14:compatExt spid="_x0000_s2052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1134,13 +1553,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1041" name="Spinner 17" hidden="1">
+            <xdr:cNvPr id="2053" name="Spinner 5" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1041"/>
+                  <a14:compatExt spid="_x0000_s2053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1184,13 +1603,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1042" name="Spinner 18" hidden="1">
+            <xdr:cNvPr id="2054" name="Spinner 6" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1042"/>
+                  <a14:compatExt spid="_x0000_s2054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1234,13 +1653,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1043" name="Spinner 19" hidden="1">
+            <xdr:cNvPr id="2055" name="Spinner 7" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1043"/>
+                  <a14:compatExt spid="_x0000_s2055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1284,13 +1703,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1044" name="Spinner 20" hidden="1">
+            <xdr:cNvPr id="2056" name="Spinner 8" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
+                  <a14:compatExt spid="_x0000_s2056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1334,13 +1753,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1045" name="Spinner 21" hidden="1">
+            <xdr:cNvPr id="2057" name="Spinner 9" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
+                  <a14:compatExt spid="_x0000_s2057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1384,13 +1803,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1046" name="Spinner 22" hidden="1">
+            <xdr:cNvPr id="2058" name="Spinner 10" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
+                  <a14:compatExt spid="_x0000_s2058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1434,13 +1853,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1047" name="Spinner 23" hidden="1">
+            <xdr:cNvPr id="2059" name="Spinner 11" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
+                  <a14:compatExt spid="_x0000_s2059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000017040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1484,13 +1903,13 @@
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="1048" name="Spinner 24" hidden="1">
+            <xdr:cNvPr id="2060" name="Spinner 12" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
+                  <a14:compatExt spid="_x0000_s2060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000018040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C080000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1546,7 +1965,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5067300" y="933450"/>
+          <a:off x="5067300" y="3416300"/>
           <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1591,7 +2010,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5067300" y="1117600"/>
+          <a:off x="5067300" y="3784600"/>
           <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1636,7 +2055,7 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="5067300" y="1301750"/>
+          <a:off x="5067300" y="3968750"/>
           <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1681,6 +2100,1696 @@
       </xdr:nvSpPr>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
+          <a:off x="5067300" y="4152900"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Spinner 6" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="4337050"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2061" name="Spinner 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2061"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2062" name="Spinner 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2063" name="Spinner 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2064" name="Spinner 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2065" name="Spinner 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000011080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2066" name="Spinner 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000012080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2067" name="Spinner 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000013080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2068" name="Spinner 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000014080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2069" name="Spinner 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2070" name="Spinner 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000016080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="Spinner 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000001040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="Spinner 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1027" name="Spinner 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1028" name="Spinner 4" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1029" name="Spinner 5" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1029"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1030" name="Spinner 6" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1031" name="Spinner 7" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1031"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1032" name="Spinner 8" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1032"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1036" name="Spinner 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1036"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1037" name="Spinner 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1037"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>19050</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>6350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1038" name="Spinner 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1038"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000E040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1040" name="Spinner 16" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1040"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1041" name="Spinner 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1041"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000011040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1042" name="Spinner 18" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1042"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1043" name="Spinner 19" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1043"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1044" name="Spinner 20" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1044"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1045" name="Spinner 21" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1045"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1046" name="Spinner 22" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1046"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1047" name="Spinner 23" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1047"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1048" name="Spinner 24" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1048"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="Spinner 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="933450"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Spinner 2" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1026"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1117600"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Spinner 3" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1027"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="1301750"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Spinner 4" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1028"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
           <a:off x="5067300" y="1485900"/>
           <a:ext cx="177800" cy="171450"/>
         </a:xfrm>
@@ -1718,7 +3827,7 @@
               <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1030"/>
             </a:ext>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1765,7 +3874,7 @@
                   <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000039040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000039040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1815,7 +3924,7 @@
                   <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003A040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003A040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1865,7 +3974,7 @@
                   <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003B040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003B040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1915,7 +4024,7 @@
                   <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003C040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003C040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1965,7 +4074,7 @@
                   <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003D040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00003D040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2015,7 +4124,7 @@
                   <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000041040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2065,7 +4174,7 @@
                   <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000042040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2115,7 +4224,7 @@
                   <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000043040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000043040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2165,7 +4274,7 @@
                   <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000044040000}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000044040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2215,7 +4324,102 @@
                   <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A98AC2B7-CDF6-EFF3-0CAD-A82E060FDC72}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000045040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Spinner 1" hidden="1">
+          <a:extLst>
+            <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+              <a14:compatExt xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" spid="_x0000_s1025"/>
+            </a:ext>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5067300" y="933450"/>
+          <a:ext cx="177800" cy="171450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:miter lim="800000"/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>6350</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>12700</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1094" name="Spinner 70" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000046040000}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2565,7 +4769,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3D32E-9FFB-480D-9074-7649C0A05B73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61521B00-E4D2-4533-B2EC-59F877E0D046}">
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2581,30 +4785,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="28">
+      <c r="B2" s="37"/>
+      <c r="C2" s="38">
         <v>45491</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="30"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -2844,16 +5048,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -3007,17 +5211,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -3115,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="16">
-        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
+        <f t="shared" ref="H28:H30" si="2">(E28*F28)+G28</f>
         <v>0</v>
       </c>
       <c r="I28" s="18">
@@ -3140,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="16">
-        <f t="shared" ref="H29:H30" si="3">(E29*F29)+G29</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I29" s="18">
@@ -3165,7 +5369,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I30" s="18">
@@ -3182,18 +5386,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="F33" s="20" t="s">
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="F33" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="22"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -3203,17 +5407,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="42">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="34"/>
+      <c r="D34" s="42"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="31" t="s">
+      <c r="G34" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="33"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="45"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -3223,14 +5427,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="31" t="s">
+      <c r="G35" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="33"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="45"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -3240,14 +5444,14 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="31" t="s">
+      <c r="G36" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="32"/>
-      <c r="I36" s="33"/>
+      <c r="H36" s="44"/>
+      <c r="I36" s="45"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -3257,14 +5461,14 @@
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="31" t="s">
+      <c r="G37" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="33"/>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -3273,8 +5477,8 @@
       <c r="B38" s="6">
         <v>0</v>
       </c>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3292,11 +5496,1439 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="G35:I35"/>
     <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A24:I24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{B77930E6-A6AA-4ED0-A544-D8AC245535CE}"/>
+    <hyperlink ref="B41" r:id="rId2" xr:uid="{716ECD04-4A4A-4438-936D-1D68C17EC2D4}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+  <legacyDrawing r:id="rId5"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x14">
+      <controls>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2049" r:id="rId6" name="Spinner 1">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2050" r:id="rId7" name="Spinner 2">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2051" r:id="rId8" name="Spinner 3">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2052" r:id="rId9" name="Spinner 4">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>5</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2053" r:id="rId10" name="Spinner 5">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2054" r:id="rId11" name="Spinner 6">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2055" r:id="rId12" name="Spinner 7">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2056" r:id="rId13" name="Spinner 8">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>10</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2057" r:id="rId14" name="Spinner 9">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>11</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2058" r:id="rId15" name="Spinner 10">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2059" r:id="rId16" name="Spinner 11">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2060" r:id="rId17" name="Spinner 12">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2061" r:id="rId18" name="Spinner 13">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>16</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2062" r:id="rId19" name="Spinner 14">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2063" r:id="rId20" name="Spinner 15">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2064" r:id="rId21" name="Spinner 16">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2065" r:id="rId22" name="Spinner 17">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2066" r:id="rId23" name="Spinner 18">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>8</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>9</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2067" r:id="rId24" name="Spinner 19">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>17</xdr:row>
+                    <xdr:rowOff>19050</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>18</xdr:row>
+                    <xdr:rowOff>6350</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2068" r:id="rId25" name="Spinner 20">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2069" r:id="rId26" name="Spinner 21">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="2070" r:id="rId27" name="Spinner 22">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>12</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>13</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+      </controls>
+    </mc:Choice>
+  </mc:AlternateContent>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AF3D32E-9FFB-480D-9074-7649C0A05B73}">
+  <dimension ref="A1:Q41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.81640625" customWidth="1"/>
+    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="3" max="3" width="6.26953125" customWidth="1"/>
+    <col min="4" max="4" width="4.36328125" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" customWidth="1"/>
+    <col min="6" max="6" width="9.90625" customWidth="1"/>
+    <col min="7" max="7" width="9.1796875" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" customWidth="1"/>
+    <col min="9" max="9" width="9.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38">
+        <v>45491</v>
+      </c>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="40"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="47" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="20"/>
+      <c r="B4" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="25">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26">
+        <v>145.88999999999999</v>
+      </c>
+      <c r="G4" s="29">
+        <v>2.04</v>
+      </c>
+      <c r="H4" s="16">
+        <f>(E4*F4)+G4</f>
+        <v>147.92999999999998</v>
+      </c>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="20"/>
+      <c r="B5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="25">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26">
+        <v>0</v>
+      </c>
+      <c r="G5" s="27">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="25">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="26">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="20"/>
+      <c r="B8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="25">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0</v>
+      </c>
+      <c r="G8" s="27">
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="51" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="51"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="20"/>
+      <c r="B9" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="25">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26">
+        <v>0</v>
+      </c>
+      <c r="G10" s="27">
+        <v>0</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+      <c r="N10" s="53"/>
+      <c r="O10" s="53"/>
+      <c r="P10" s="53"/>
+      <c r="Q10" s="53"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
+      <c r="B11" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="25">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26">
+        <v>0</v>
+      </c>
+      <c r="G11" s="27">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="20"/>
+      <c r="B12" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="25">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26">
+        <v>0</v>
+      </c>
+      <c r="G12" s="27">
+        <v>0</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="20"/>
+      <c r="B13" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="25">
+        <v>0</v>
+      </c>
+      <c r="F13" s="26">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="25">
+        <v>0</v>
+      </c>
+      <c r="F17" s="26">
+        <v>0</v>
+      </c>
+      <c r="G17" s="27">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <f>(E17*F17)+G17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="55"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="55"/>
+      <c r="Q17" s="55"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="25">
+        <v>0</v>
+      </c>
+      <c r="F18" s="26">
+        <v>0</v>
+      </c>
+      <c r="G18" s="27">
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <v>0</v>
+      </c>
+      <c r="K18" s="19"/>
+      <c r="L18" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="M18" s="55"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="55"/>
+      <c r="P18" s="55"/>
+      <c r="Q18" s="55"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="25">
+        <v>0</v>
+      </c>
+      <c r="F19" s="26">
+        <v>0</v>
+      </c>
+      <c r="G19" s="27">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" ref="H19:H22" si="1">(E19*F19)+G19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="25">
+        <v>0</v>
+      </c>
+      <c r="F20" s="26">
+        <v>0</v>
+      </c>
+      <c r="G20" s="27">
+        <v>0</v>
+      </c>
+      <c r="H20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="25">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="25">
+        <v>0</v>
+      </c>
+      <c r="F22" s="26">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+      <c r="K24" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="56"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="59"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="20"/>
+      <c r="B26" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="25">
+        <v>0</v>
+      </c>
+      <c r="F26" s="28">
+        <v>0</v>
+      </c>
+      <c r="G26" s="27">
+        <v>0</v>
+      </c>
+      <c r="H26" s="16">
+        <f>(E26*F26)+G26</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="18">
+        <f>H26-H4</f>
+        <v>-147.92999999999998</v>
+      </c>
+      <c r="K26" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="61"/>
+      <c r="M26" s="61"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="61"/>
+      <c r="P26" s="61"/>
+      <c r="Q26" s="62"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="25">
+        <v>0</v>
+      </c>
+      <c r="F27" s="26">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
+        <f>(E27*F27)+G27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="18">
+        <f>H27-0</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="63" t="s">
+        <v>62</v>
+      </c>
+      <c r="L27" s="64"/>
+      <c r="M27" s="64"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="64"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="65"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="20"/>
+      <c r="B28" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="22"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="25">
+        <v>0</v>
+      </c>
+      <c r="F28" s="26">
+        <v>0</v>
+      </c>
+      <c r="G28" s="27">
+        <v>0</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" ref="H28" si="2">(E28*F28)+G28</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <f t="shared" ref="I28:I30" si="3">H28-0</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="63" t="s">
+        <v>63</v>
+      </c>
+      <c r="L28" s="64"/>
+      <c r="M28" s="64"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="64"/>
+      <c r="P28" s="64"/>
+      <c r="Q28" s="65"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="20"/>
+      <c r="B29" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="25">
+        <v>0</v>
+      </c>
+      <c r="F29" s="26">
+        <v>0</v>
+      </c>
+      <c r="G29" s="27">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" ref="H29:H30" si="4">(E29*F29)+G29</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="65"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30" s="20"/>
+      <c r="B30" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="25">
+        <v>0</v>
+      </c>
+      <c r="F30" s="26">
+        <v>0</v>
+      </c>
+      <c r="G30" s="27">
+        <v>0</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="I30" s="18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="L30" s="64"/>
+      <c r="M30" s="64"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="64"/>
+      <c r="P30" s="64"/>
+      <c r="Q30" s="65"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="K31" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="67"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="68"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="C32" s="4"/>
+      <c r="I32" s="5"/>
+      <c r="K32" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="L32" s="70"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="70"/>
+      <c r="O32" s="70"/>
+      <c r="P32" s="70"/>
+      <c r="Q32" s="71"/>
+    </row>
+    <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="F33" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="33"/>
+    </row>
+    <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="46"/>
+      <c r="D34" s="46"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="44"/>
+      <c r="I34" s="45"/>
+    </row>
+    <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="44"/>
+      <c r="I35" s="45"/>
+    </row>
+    <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36" s="44"/>
+      <c r="I36" s="45"/>
+    </row>
+    <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="44"/>
+      <c r="I37" s="45"/>
+    </row>
+    <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+    </row>
+    <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A33:D33"/>
@@ -3304,6 +6936,11 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
@@ -3800,6 +7437,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId28" name="Spinner 70">
+              <controlPr defaultSize="0" autoPict="0">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>6350</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>12700</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>184150</xdr:colOff>
+                    <xdr:row>4</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/assets/downloads/CONFIG MAKER EN by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER EN by KJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1016" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42E49BA0-BE8A-46BA-B734-9407F93AB60C}"/>
+  <xr:revisionPtr revIDLastSave="1033" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61569485-E8A6-43AC-8761-B30D3D25F96E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="74">
   <si>
     <t>Total</t>
   </si>
@@ -257,13 +257,17 @@
   <si>
     <t>INSTRUCTION MANUAL</t>
   </si>
+  <si>
+    <t>CONFIG MAKER v2024.7.29</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[Red]\▲\ 0.00;[Green]\ \▼\ 0.00"/>
+    <numFmt numFmtId="165" formatCode="[Red]\▲\ 0.00;[Color50]\ \▼\ 0.00"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -597,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -653,6 +657,21 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,69 +705,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -776,12 +732,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4785,30 +4854,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38">
-        <v>45491</v>
-      </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
+        <v>45502</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5048,16 +5117,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5211,17 +5280,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -5272,8 +5341,8 @@
         <f>(E26*F26)+G26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="18">
-        <f>H26-H4</f>
+      <c r="I26" s="73">
+        <f>H26-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5297,8 +5366,8 @@
         <f>(E27*F27)+G27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="18">
-        <f>H27-H10</f>
+      <c r="I27" s="73">
+        <f>H27-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5322,8 +5391,8 @@
         <f t="shared" ref="H28:H30" si="2">(E28*F28)+G28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="18">
-        <f>H28-H10</f>
+      <c r="I28" s="73">
+        <f t="shared" ref="I27:I30" si="3">H28-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5347,8 +5416,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="18">
-        <f>H29-H11</f>
+      <c r="I29" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5372,8 +5441,8 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I30" s="18">
-        <f>H30-H12</f>
+      <c r="I30" s="73">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5386,18 +5455,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="F33" s="31" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="F33" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -5407,17 +5476,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="42">
+      <c r="C34" s="31">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="42"/>
+      <c r="D34" s="31"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="43" t="s">
+      <c r="G34" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="44"/>
-      <c r="I34" s="45"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="34"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -5427,14 +5496,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="43" t="s">
+      <c r="G35" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -5444,31 +5513,31 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="43" t="s">
+      <c r="G36" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="34"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="30">
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="43" t="s">
+      <c r="G37" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="44"/>
-      <c r="I37" s="45"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="34"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -5477,13 +5546,13 @@
       <c r="B38" s="6">
         <v>0</v>
       </c>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="14" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>15</v>
@@ -5496,11 +5565,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C34:D38"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A1:H1"/>
@@ -5508,7 +5572,23 @@
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
   </mergeCells>
+  <conditionalFormatting sqref="B37">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>$B$38</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>$B$38</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{B77930E6-A6AA-4ED0-A544-D8AC245535CE}"/>
     <hyperlink ref="B41" r:id="rId2" xr:uid="{716ECD04-4A4A-4438-936D-1D68C17EC2D4}"/>
@@ -6027,30 +6107,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38">
+      <c r="B2" s="42"/>
+      <c r="C2" s="43">
         <v>45491</v>
       </c>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="40"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6078,15 +6158,15 @@
         <v>0</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" s="47" t="s">
+      <c r="K3" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="68"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="20"/>
@@ -6108,13 +6188,13 @@
         <f>(E4*F4)+G4</f>
         <v>147.92999999999998</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="68"/>
+      <c r="Q4" s="68"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="20"/>
@@ -6136,15 +6216,15 @@
         <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="48" t="s">
+      <c r="K5" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="48"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="48"/>
-      <c r="P5" s="48"/>
-      <c r="Q5" s="48"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="20"/>
@@ -6166,15 +6246,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="49" t="s">
+      <c r="K6" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="49"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="70"/>
+      <c r="Q6" s="70"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="20"/>
@@ -6196,15 +6276,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="50" t="s">
+      <c r="K7" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="20"/>
@@ -6226,15 +6306,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="51" t="s">
+      <c r="K8" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
+      <c r="L8" s="64"/>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="20"/>
@@ -6256,15 +6336,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="52" t="s">
+      <c r="K9" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="52"/>
-      <c r="M9" s="52"/>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
-      <c r="Q9" s="52"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="20"/>
@@ -6286,15 +6366,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="53" t="s">
+      <c r="K10" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
@@ -6316,15 +6396,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="54" t="s">
+      <c r="K11" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="20"/>
@@ -6369,16 +6449,16 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -6428,14 +6508,14 @@
         <v>0</v>
       </c>
       <c r="K17" s="16"/>
-      <c r="L17" s="55" t="s">
+      <c r="L17" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="M17" s="55"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="55"/>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="20"/>
@@ -6457,14 +6537,14 @@
         <v>0</v>
       </c>
       <c r="K18" s="19"/>
-      <c r="L18" s="55" t="s">
+      <c r="L18" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="M18" s="55"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="55"/>
-      <c r="P18" s="55"/>
-      <c r="Q18" s="55"/>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="20"/>
@@ -6550,26 +6630,26 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="41" t="s">
+      <c r="A24" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="K24" s="56" t="s">
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="K24" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="56"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="56"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="57"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -6599,15 +6679,15 @@
       <c r="I25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K25" s="57" t="s">
+      <c r="K25" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="59"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="59"/>
+      <c r="N25" s="59"/>
+      <c r="O25" s="59"/>
+      <c r="P25" s="59"/>
+      <c r="Q25" s="60"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="20"/>
@@ -6633,15 +6713,15 @@
         <f>H26-H4</f>
         <v>-147.92999999999998</v>
       </c>
-      <c r="K26" s="60" t="s">
+      <c r="K26" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="L26" s="61"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="61"/>
-      <c r="P26" s="61"/>
-      <c r="Q26" s="62"/>
+      <c r="L26" s="62"/>
+      <c r="M26" s="62"/>
+      <c r="N26" s="62"/>
+      <c r="O26" s="62"/>
+      <c r="P26" s="62"/>
+      <c r="Q26" s="63"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="20"/>
@@ -6667,15 +6747,15 @@
         <f>H27-0</f>
         <v>0</v>
       </c>
-      <c r="K27" s="63" t="s">
+      <c r="K27" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="64"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="64"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="49"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="20"/>
@@ -6701,15 +6781,15 @@
         <f t="shared" ref="I28:I30" si="3">H28-0</f>
         <v>0</v>
       </c>
-      <c r="K28" s="63" t="s">
+      <c r="K28" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="L28" s="64"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="64"/>
-      <c r="O28" s="64"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="49"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
@@ -6735,15 +6815,15 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K29" s="63" t="s">
+      <c r="K29" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="64"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="64"/>
-      <c r="O29" s="64"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="49"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
@@ -6769,55 +6849,55 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="63" t="s">
+      <c r="K30" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="L30" s="64"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="64"/>
-      <c r="O30" s="64"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="49"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
-      <c r="K31" s="66" t="s">
+      <c r="K31" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="68"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="52"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C32" s="4"/>
       <c r="I32" s="5"/>
-      <c r="K32" s="69" t="s">
+      <c r="K32" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="70"/>
-      <c r="O32" s="70"/>
-      <c r="P32" s="70"/>
-      <c r="Q32" s="71"/>
+      <c r="L32" s="54"/>
+      <c r="M32" s="54"/>
+      <c r="N32" s="54"/>
+      <c r="O32" s="54"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="55"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="F33" s="31" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="F33" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="33"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -6826,14 +6906,14 @@
       <c r="B34" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="46"/>
-      <c r="D34" s="46"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="43" t="s">
+      <c r="G34" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="44"/>
-      <c r="I34" s="45"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="34"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -6842,14 +6922,14 @@
       <c r="B35" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="43" t="s">
+      <c r="G35" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -6858,14 +6938,14 @@
       <c r="B36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="43" t="s">
+      <c r="G36" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="34"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -6874,14 +6954,14 @@
       <c r="B37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="43" t="s">
+      <c r="G37" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="44"/>
-      <c r="I37" s="45"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="34"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -6890,8 +6970,8 @@
       <c r="B38" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="46"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6909,26 +6989,11 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="K11:Q11"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="K7:Q7"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A33:D33"/>
@@ -6936,11 +7001,26 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K7:Q7"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="K32:Q32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>

--- a/assets/downloads/CONFIG MAKER EN by KJ.xlsx
+++ b/assets/downloads/CONFIG MAKER EN by KJ.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epitafr-my.sharepoint.com/personal/kevin_jamet_epita_fr/Documents/Others/Configs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1033" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61569485-E8A6-43AC-8761-B30D3D25F96E}"/>
+  <xr:revisionPtr revIDLastSave="1049" documentId="8_{6424AB06-F752-47B9-BCE5-9360DAAD03EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7802A48-4B8A-4D5B-B0A9-08BFD83183D4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{8947F335-7243-4BC9-9D88-00188AB47FC0}"/>
   </bookViews>
@@ -258,7 +258,7 @@
     <t>INSTRUCTION MANUAL</t>
   </si>
   <si>
-    <t>CONFIG MAKER v2024.7.29</t>
+    <t>CONFIG MAKER v2024.8.9</t>
   </si>
 </sst>
 </file>
@@ -657,18 +657,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -705,6 +694,66 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -732,64 +781,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -817,36 +817,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4844,8 +4814,7 @@
   <cols>
     <col min="1" max="1" width="5.81640625" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="6.26953125" customWidth="1"/>
-    <col min="4" max="4" width="4.36328125" customWidth="1"/>
+    <col min="3" max="4" width="6.6328125" customWidth="1"/>
     <col min="5" max="5" width="10.08984375" customWidth="1"/>
     <col min="6" max="6" width="9.90625" customWidth="1"/>
     <col min="7" max="7" width="9.1796875" customWidth="1"/>
@@ -4854,30 +4823,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43">
-        <v>45502</v>
-      </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="40">
+        <v>45513</v>
+      </c>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -5117,16 +5086,16 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
@@ -5280,17 +5249,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -5341,7 +5310,7 @@
         <f>(E26*F26)+G26</f>
         <v>0</v>
       </c>
-      <c r="I26" s="73">
+      <c r="I26" s="31">
         <f>H26-0</f>
         <v>0</v>
       </c>
@@ -5366,7 +5335,7 @@
         <f>(E27*F27)+G27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="73">
+      <c r="I27" s="31">
         <f>H27-0</f>
         <v>0</v>
       </c>
@@ -5391,8 +5360,8 @@
         <f t="shared" ref="H28:H30" si="2">(E28*F28)+G28</f>
         <v>0</v>
       </c>
-      <c r="I28" s="73">
-        <f t="shared" ref="I27:I30" si="3">H28-0</f>
+      <c r="I28" s="31">
+        <f t="shared" ref="I28:I30" si="3">H28-0</f>
         <v>0</v>
       </c>
     </row>
@@ -5416,7 +5385,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I29" s="73">
+      <c r="I29" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5441,7 +5410,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I30" s="73">
+      <c r="I30" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5455,18 +5424,18 @@
       <c r="I32" s="5"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="F33" s="36" t="s">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="F33" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="38"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -5476,17 +5445,17 @@
         <f>SUM(H4:H12)</f>
         <v>0</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="73">
         <f>B37-B38</f>
         <v>0</v>
       </c>
-      <c r="D34" s="31"/>
+      <c r="D34" s="73"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="46"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -5496,14 +5465,14 @@
         <f>SUM(H17:H22)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="34"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="46"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -5513,14 +5482,14 @@
         <f>SUM(H26:H30)</f>
         <v>0</v>
       </c>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="34"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -5530,14 +5499,14 @@
         <f>B34+B35+B36</f>
         <v>0</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="34"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="46"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -5546,8 +5515,8 @@
       <c r="B38" s="6">
         <v>0</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5565,6 +5534,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G37:I37"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A1:H1"/>
@@ -5572,20 +5546,15 @@
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="C34:D38"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G37:I37"/>
   </mergeCells>
   <conditionalFormatting sqref="B37">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>$B$38</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>$B$38</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThan">
       <formula>$B$38</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6107,30 +6076,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43">
+      <c r="B2" s="39"/>
+      <c r="C2" s="40">
         <v>45491</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="45"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -6158,15 +6127,15 @@
         <v>0</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="20"/>
@@ -6188,13 +6157,13 @@
         <f>(E4*F4)+G4</f>
         <v>147.92999999999998</v>
       </c>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
-      <c r="Q4" s="68"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="20"/>
@@ -6216,15 +6185,15 @@
         <f t="shared" ref="H5:H13" si="0">(E5*F5)+G5</f>
         <v>0</v>
       </c>
-      <c r="K5" s="69" t="s">
+      <c r="K5" s="49" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="69"/>
-      <c r="P5" s="69"/>
-      <c r="Q5" s="69"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="20"/>
@@ -6246,15 +6215,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K6" s="70" t="s">
+      <c r="K6" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="L6" s="70"/>
-      <c r="M6" s="70"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="50"/>
+      <c r="Q6" s="50"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="20"/>
@@ -6276,15 +6245,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K7" s="71" t="s">
+      <c r="K7" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="51"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="20"/>
@@ -6306,15 +6275,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K8" s="64" t="s">
+      <c r="K8" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="64"/>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
+      <c r="L8" s="52"/>
+      <c r="M8" s="52"/>
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="52"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="20"/>
@@ -6336,15 +6305,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K9" s="65" t="s">
+      <c r="K9" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="65"/>
-      <c r="M9" s="65"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="65"/>
-      <c r="Q9" s="65"/>
+      <c r="L9" s="53"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="53"/>
+      <c r="P9" s="53"/>
+      <c r="Q9" s="53"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="20"/>
@@ -6366,15 +6335,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K10" s="66" t="s">
+      <c r="K10" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="66"/>
-      <c r="M10" s="66"/>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
+      <c r="L10" s="54"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="54"/>
+      <c r="O10" s="54"/>
+      <c r="P10" s="54"/>
+      <c r="Q10" s="54"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="20"/>
@@ -6396,15 +6365,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="67" t="s">
+      <c r="K11" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="67"/>
-      <c r="M11" s="67"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
-      <c r="Q11" s="67"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="55"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="20"/>
@@ -6449,16 +6418,16 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
       <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -6630,17 +6599,17 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
       <c r="K24" s="57" t="s">
         <v>60</v>
       </c>
@@ -6747,15 +6716,15 @@
         <f>H27-0</f>
         <v>0</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="49"/>
+      <c r="L27" s="65"/>
+      <c r="M27" s="65"/>
+      <c r="N27" s="65"/>
+      <c r="O27" s="65"/>
+      <c r="P27" s="65"/>
+      <c r="Q27" s="66"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="20"/>
@@ -6781,15 +6750,15 @@
         <f t="shared" ref="I28:I30" si="3">H28-0</f>
         <v>0</v>
       </c>
-      <c r="K28" s="47" t="s">
+      <c r="K28" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="49"/>
+      <c r="L28" s="65"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="65"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="66"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="20"/>
@@ -6815,15 +6784,15 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K29" s="47" t="s">
+      <c r="K29" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="49"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="65"/>
+      <c r="P29" s="65"/>
+      <c r="Q29" s="66"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="20"/>
@@ -6849,55 +6818,55 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K30" s="47" t="s">
+      <c r="K30" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="L30" s="48"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="49"/>
+      <c r="L30" s="65"/>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="66"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="I31" s="5"/>
-      <c r="K31" s="50" t="s">
+      <c r="K31" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="52"/>
+      <c r="L31" s="68"/>
+      <c r="M31" s="68"/>
+      <c r="N31" s="68"/>
+      <c r="O31" s="68"/>
+      <c r="P31" s="68"/>
+      <c r="Q31" s="69"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="C32" s="4"/>
       <c r="I32" s="5"/>
-      <c r="K32" s="53" t="s">
+      <c r="K32" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L32" s="54"/>
-      <c r="M32" s="54"/>
-      <c r="N32" s="54"/>
-      <c r="O32" s="54"/>
-      <c r="P32" s="54"/>
-      <c r="Q32" s="55"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="72"/>
     </row>
     <row r="33" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="F33" s="36" t="s">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="F33" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="38"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="35"/>
     </row>
     <row r="34" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
@@ -6906,14 +6875,14 @@
       <c r="B34" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="46"/>
     </row>
     <row r="35" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
@@ -6922,14 +6891,14 @@
       <c r="B35" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="34"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="46"/>
     </row>
     <row r="36" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
@@ -6938,14 +6907,14 @@
       <c r="B36" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
       <c r="F36" s="9"/>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="34"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="46"/>
     </row>
     <row r="37" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
@@ -6954,14 +6923,14 @@
       <c r="B37" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
       <c r="F37" s="10"/>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="34"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="46"/>
     </row>
     <row r="38" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
@@ -6970,8 +6939,8 @@
       <c r="B38" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
     </row>
     <row r="39" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6989,11 +6958,26 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="K28:Q28"/>
+    <mergeCell ref="K29:Q29"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="K31:Q31"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="L18:Q18"/>
+    <mergeCell ref="K24:Q24"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="K11:Q11"/>
+    <mergeCell ref="L17:Q17"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="K6:Q6"/>
+    <mergeCell ref="K7:Q7"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="F33:I33"/>
     <mergeCell ref="A33:D33"/>
@@ -7001,26 +6985,11 @@
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="K4:Q4"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="K6:Q6"/>
-    <mergeCell ref="K7:Q7"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="K11:Q11"/>
-    <mergeCell ref="L17:Q17"/>
-    <mergeCell ref="L18:Q18"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="K28:Q28"/>
-    <mergeCell ref="K29:Q29"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="C34:D38"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C40" r:id="rId1" xr:uid="{5ACE79AC-C4D3-4369-9A50-83248646C37E}"/>
